--- a/Old/Results_Original_Submission/Alarm Fatigue.xlsx
+++ b/Old/Results_Original_Submission/Alarm Fatigue.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -36,15 +36,6 @@
   </si>
   <si>
     <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
   </si>
 </sst>
 </file>
@@ -419,75 +410,6 @@
         <v>276</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="n">
-        <v>6752</v>
-      </c>
-      <c r="C3" t="n">
-        <v>947</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5805</v>
-      </c>
-      <c r="E3" t="n">
-        <v>225</v>
-      </c>
-      <c r="F3" t="n">
-        <v>32</v>
-      </c>
-      <c r="G3" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5636</v>
-      </c>
-      <c r="C4" t="n">
-        <v>874</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4762</v>
-      </c>
-      <c r="E4" t="n">
-        <v>188</v>
-      </c>
-      <c r="F4" t="n">
-        <v>29</v>
-      </c>
-      <c r="G4" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4676</v>
-      </c>
-      <c r="C5" t="n">
-        <v>816</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3860</v>
-      </c>
-      <c r="E5" t="n">
-        <v>156</v>
-      </c>
-      <c r="F5" t="n">
-        <v>27</v>
-      </c>
-      <c r="G5" t="n">
-        <v>129</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Old/Results_Original_Submission/Alarm Fatigue.xlsx
+++ b/Old/Results_Original_Submission/Alarm Fatigue.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -36,6 +36,15 @@
   </si>
   <si>
     <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
   </si>
 </sst>
 </file>
@@ -410,6 +419,75 @@
         <v>276</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6752</v>
+      </c>
+      <c r="C3" t="n">
+        <v>947</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5805</v>
+      </c>
+      <c r="E3" t="n">
+        <v>225</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5636</v>
+      </c>
+      <c r="C4" t="n">
+        <v>874</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4762</v>
+      </c>
+      <c r="E4" t="n">
+        <v>188</v>
+      </c>
+      <c r="F4" t="n">
+        <v>29</v>
+      </c>
+      <c r="G4" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4676</v>
+      </c>
+      <c r="C5" t="n">
+        <v>816</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3860</v>
+      </c>
+      <c r="E5" t="n">
+        <v>156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
